--- a/output/pdf_financials_xlsx/ZZE.H.xlsx
+++ b/output/pdf_financials_xlsx/ZZE.H.xlsx
@@ -5792,49 +5792,49 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.053458</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.053458</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.053458</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.053458</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.053458</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.053458</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
     </row>
     <row r="93">
@@ -9336,7 +9336,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ZZE.H.xlsx
+++ b/output/pdf_financials_xlsx/ZZE.H.xlsx
@@ -1050,25 +1050,25 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003036</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003653</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003007</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002975</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002585</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00068</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000458</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -2029,25 +2029,25 @@
         <v>-0.000851</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.130353</v>
+        <v>-0.133389</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.040791</v>
+        <v>-0.044444</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.046898</v>
+        <v>-0.049905</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.032892</v>
+        <v>-0.035867</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.044342</v>
+        <v>-0.046927</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.094814</v>
+        <v>-0.095494</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.122897</v>
+        <v>-0.123355</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2151,25 +2151,25 @@
         <v>-0.000851</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.130353</v>
+        <v>-0.133389</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.040791</v>
+        <v>-0.044444</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.046898</v>
+        <v>-0.049905</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.032892</v>
+        <v>-0.035867</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.044342</v>
+        <v>-0.046927</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.094814</v>
+        <v>-0.095494</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.122897</v>
+        <v>-0.123355</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZZE.H.xlsx
+++ b/output/pdf_financials_xlsx/ZZE.H.xlsx
@@ -582,20 +582,14 @@
       <c r="I4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
@@ -643,20 +637,14 @@
       <c r="I5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
@@ -704,20 +692,14 @@
       <c r="I6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
@@ -765,20 +747,14 @@
       <c r="I7" s="3" t="n">
         <v>0.010446</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J7" s="3" t="n">
+        <v>0.010115</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.015076</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.011519</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0.012985</v>
@@ -826,20 +802,14 @@
       <c r="I8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>0</v>
@@ -887,20 +857,14 @@
       <c r="I9" s="3" t="n">
         <v>0.103206</v>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J9" s="3" t="n">
+        <v>0.04914</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.042848</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.029942</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>0.004011</v>
@@ -948,20 +912,14 @@
       <c r="I10" s="3" t="n">
         <v>0.113652</v>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J10" s="3" t="n">
+        <v>0.059255</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.057924</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.041461</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.016996</v>
@@ -1009,20 +967,14 @@
       <c r="I11" s="3" t="n">
         <v>-0.123355</v>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J11" s="3" t="n">
+        <v>-0.06938800000000001</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-0.06632399999999999</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-0.041461</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>-0.016996</v>
@@ -1070,20 +1022,14 @@
       <c r="I12" s="3" t="n">
         <v>0.000458</v>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J12" s="3" t="n">
+        <v>5.1e-05</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1131,20 +1077,14 @@
       <c r="I13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>-0</v>
@@ -1192,20 +1132,14 @@
       <c r="I14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0</v>
@@ -1253,20 +1187,14 @@
       <c r="I15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0</v>
@@ -1314,20 +1242,14 @@
       <c r="I16" s="3" t="n">
         <v>-0.122897</v>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J16" s="3" t="n">
+        <v>-0.069337</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>-0.06632399999999999</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>-0.051961</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-0.025496</v>
@@ -1375,20 +1297,14 @@
       <c r="I17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1610,20 +1526,14 @@
       <c r="I20" s="3" t="n">
         <v>-0.122897</v>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J20" s="3" t="n">
+        <v>-0.069337</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>-0.06632399999999999</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-0.051961</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.025496</v>
@@ -1671,20 +1581,14 @@
       <c r="I21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -1732,20 +1636,14 @@
       <c r="I22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -1793,20 +1691,14 @@
       <c r="I23" s="3" t="n">
         <v>-0.122897</v>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J23" s="3" t="n">
+        <v>-0.069337</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>-0.06632399999999999</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>-0.051961</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-0.025496</v>
@@ -1854,20 +1746,14 @@
       <c r="I24" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J24" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>0</v>
@@ -1915,20 +1801,14 @@
       <c r="I25" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J25" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>0</v>
@@ -1978,20 +1858,14 @@
       <c r="I26" s="3" t="n">
         <v>2.45794</v>
       </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J26" s="3" t="n">
+        <v>1.155617</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>1.32648</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>2.59805</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2049,20 +1923,14 @@
       <c r="I27" s="3" t="n">
         <v>-0.123355</v>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J27" s="3" t="n">
+        <v>-0.06938800000000001</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>-0.06632399999999999</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>-0.051961</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.025496</v>
@@ -2110,20 +1978,14 @@
       <c r="I28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0</v>
@@ -2171,20 +2033,14 @@
       <c r="I29" s="3" t="n">
         <v>-0.123355</v>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J29" s="3" t="n">
+        <v>-0.06938800000000001</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>-0.06632399999999999</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>-0.051961</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.025496</v>
@@ -2319,20 +2175,14 @@
       <c r="I31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -6146,25 +5996,17 @@
       <c r="H99" s="3" t="n">
         <v>-0.094814</v>
       </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="3" t="n">
+        <v>-0.122897</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>-0.069337</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>-0.06632399999999999</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>-0.051961</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-0.025496</v>
@@ -6209,25 +6051,17 @@
       <c r="H100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0</v>
@@ -6255,42 +6089,34 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005611</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.000491</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.002577</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.000838</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002124</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002061</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>-0.004163</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>0.005931</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="n">
         <v>0</v>
@@ -6302,10 +6128,10 @@
         <v>0</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001474</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>0.000467</v>
       </c>
     </row>
     <row r="102">
@@ -6335,25 +6161,17 @@
       <c r="H102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="n">
         <v>0</v>
@@ -6398,25 +6216,17 @@
       <c r="H103" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="3" t="n">
+        <v>-0.000875</v>
       </c>
       <c r="M103" s="3" t="n">
         <v>0</v>
@@ -6461,25 +6271,17 @@
       <c r="H104" s="3" t="n">
         <v>0.015159</v>
       </c>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="3" t="n">
+        <v>0.027066</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0.001014</v>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>-0.01247</v>
+      </c>
+      <c r="L104" s="3" t="n">
+        <v>-0.044257</v>
       </c>
       <c r="M104" s="3" t="n">
         <v>0.005445</v>
@@ -6524,25 +6326,17 @@
       <c r="H105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M105" s="3" t="n">
         <v>0</v>
@@ -6570,42 +6364,34 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.006764</v>
+        <v>0.001153</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.003109</v>
+        <v>0.0036</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.000884</v>
+        <v>0.001693</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.001823</v>
+        <v>-0.000985</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.015486</v>
+        <v>0.013362</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.004841</v>
-      </c>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00278</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>0.042903</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>0.006945</v>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>-0.01247</v>
+      </c>
+      <c r="L106" s="3" t="n">
+        <v>-0.045132</v>
       </c>
       <c r="M106" s="3" t="n">
         <v>0.005445</v>
@@ -6617,10 +6403,10 @@
         <v>0.001158</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0.013379</v>
+        <v>0.011905</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-0.023752</v>
+        <v>-0.023285</v>
       </c>
     </row>
     <row r="107">
@@ -6650,25 +6436,17 @@
       <c r="H107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M107" s="3" t="n">
         <v>0</v>
@@ -6713,25 +6491,17 @@
       <c r="H108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M108" s="3" t="n">
         <v>0</v>
@@ -6776,25 +6546,17 @@
       <c r="H109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M109" s="3" t="n">
         <v>0</v>
@@ -6839,25 +6601,17 @@
       <c r="H110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -6902,25 +6656,17 @@
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -6965,25 +6711,17 @@
       <c r="H112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -7028,25 +6766,17 @@
       <c r="H113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M113" s="3" t="n">
         <v>0</v>
@@ -7091,25 +6821,17 @@
       <c r="H114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>0</v>
@@ -7154,25 +6876,17 @@
       <c r="H115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -7217,25 +6931,17 @@
       <c r="H116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M116" s="3" t="n">
         <v>0</v>
@@ -7280,25 +6986,17 @@
       <c r="H117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M117" s="3" t="n">
         <v>0</v>
@@ -7343,25 +7041,17 @@
       <c r="H118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -7435,10 +7125,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M119" s="3" t="n">
         <v>0</v>
@@ -7485,25 +7173,17 @@
       <c r="H120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M120" s="3" t="n">
         <v>0</v>
@@ -7548,25 +7228,17 @@
       <c r="H121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
         <v>0</v>
@@ -7611,25 +7283,17 @@
       <c r="H122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M122" s="3" t="n">
         <v>0</v>
@@ -7674,25 +7338,17 @@
       <c r="H123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="3" t="n">
         <v>0</v>
@@ -7737,25 +7393,17 @@
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>0</v>
@@ -7800,25 +7448,17 @@
       <c r="H125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>0</v>
@@ -7863,25 +7503,17 @@
       <c r="H126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M126" s="3" t="n">
         <v>0</v>
@@ -8013,25 +7645,17 @@
       <c r="H128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>-0.001713</v>
       </c>
       <c r="M128" s="3" t="n">
         <v>-0.000614</v>
@@ -8105,10 +7729,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L129" s="3" t="n">
+        <v>0.198287</v>
       </c>
       <c r="M129" s="3" t="n">
         <v>-0.000614</v>
@@ -8155,25 +7777,17 @@
       <c r="H130" s="3" t="n">
         <v>0.200602</v>
       </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="3" t="n">
+        <v>0.163715</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0.059537</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>2.1e-05</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>0.001922</v>
       </c>
       <c r="M130" s="3" t="n">
         <v>0.01912</v>
@@ -8218,25 +7832,17 @@
       <c r="H131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M131" s="3" t="n">
         <v>0</v>
@@ -8281,25 +7887,17 @@
       <c r="H132" s="3" t="n">
         <v>-0.036887</v>
       </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I132" s="3" t="n">
+        <v>-0.104178</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>-0.059516</v>
+      </c>
+      <c r="K132" s="3" t="n">
+        <v>0.001901</v>
+      </c>
+      <c r="L132" s="3" t="n">
+        <v>0.017198</v>
       </c>
       <c r="M132" s="3" t="n">
         <v>-0.016021</v>
@@ -8344,25 +7942,17 @@
       <c r="H133" s="3" t="n">
         <v>0.163715</v>
       </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="3" t="n">
+        <v>0.059537</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>2.1e-05</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>0.001922</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>0.01912</v>
       </c>
       <c r="M133" s="3" t="n">
         <v>0.003099</v>
@@ -8407,25 +7997,17 @@
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -8489,20 +8071,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J135" s="3" t="n">
+        <v>-0.059516</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>0.001901</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>-0.181089</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-0.015407</v>
@@ -8531,7 +8107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T112"/>
+  <dimension ref="A1:T127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11170,10 +10746,8 @@
       <c r="K31" s="5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L31" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -11185,10 +10759,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O31" s="5" t="n">
+        <v>-0.000875</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -11230,7 +10802,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11256,15 +10832,11 @@
       <c r="K32" s="5" t="n">
         <v>0.002061</v>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L32" s="5" t="n">
+        <v>-0.004163</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0.005931</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -11342,25 +10914,17 @@
       <c r="K33" s="5" t="n">
         <v>0.015159</v>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L33" s="5" t="n">
+        <v>0.027066</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0.001014</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>-0.01247</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>-0.044871</v>
       </c>
       <c r="P33" s="5" t="n">
         <v>0.005445</v>
@@ -11449,10 +11013,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O34" s="5" t="n">
+        <v>-0.181089</v>
       </c>
       <c r="P34" s="5" t="n">
         <v>-0.015407</v>
@@ -12164,10 +11726,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F42" s="5" t="n">
+        <v>-0.130353</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>-0.040791</v>
@@ -12184,25 +11744,17 @@
       <c r="K42" s="5" t="n">
         <v>-0.094814</v>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L42" s="5" t="n">
+        <v>-0.122897</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>-0.069337</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>-0.06632399999999999</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>-0.051961</v>
       </c>
       <c r="P42" s="5" t="n">
         <v>-0.025496</v>
@@ -12249,10 +11801,8 @@
       <c r="F43" s="5" t="n">
         <v>0.000265</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G43" s="5" t="n">
+        <v>0.01232</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -12275,20 +11825,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M43" s="5" t="n">
+        <v>0.002687</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>0.080695</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>-0.083382</v>
       </c>
       <c r="P43" s="5" t="n">
         <v>0.004644</v>
@@ -12362,25 +11906,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L44" s="5" t="n">
+        <v>-0.104178</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>-0.059516</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0.001901</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0.017198</v>
       </c>
       <c r="P44" s="5" t="n">
         <v>-0.016021</v>
@@ -12450,25 +11986,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L45" s="5" t="n">
+        <v>0.163715</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0.059537</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>2.1e-05</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>0.001922</v>
       </c>
       <c r="P45" s="5" t="n">
         <v>0.01912</v>
@@ -12538,25 +12066,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L46" s="5" t="n">
+        <v>0.059537</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>2.1e-05</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>0.001922</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0.01912</v>
       </c>
       <c r="P46" s="5" t="n">
         <v>0.003099</v>
@@ -12649,10 +12169,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O47" s="5" t="n">
+        <v>-0.001713</v>
       </c>
       <c r="P47" s="5" t="n">
         <v>-0.000614</v>
@@ -12791,7 +12309,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Interest receivable</t>
+          <t>Shares issued</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -12800,25 +12318,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F49" s="5" t="n">
-        <v>-0.003036</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H49" s="5" t="n">
-        <v>0.000405</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>-8.4e-05</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>0.000225</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>0.001217</v>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -12835,10 +12363,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O49" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -12879,10 +12405,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Total cash (used in) provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -12893,22 +12423,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n">
-        <v>0.01232</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>0.01274</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J50" s="5" t="n">
-        <v>-0.0124</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>-0.00281</v>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -12925,15 +12463,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O50" s="5" t="n">
+        <v>0.198287</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>-0.000614</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -12969,30 +12503,48 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Total cash outflows from operating activities</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
-        <v>-0.000851</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>-0.084343</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.024223</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>-0.03206</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>-0.021361</v>
-      </c>
-      <c r="J51" s="5" t="n">
-        <v>-0.043155</v>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>-0.099187</v>
+          <t>Share issue costs included in accounts payable and accrued liabilities $</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -13009,10 +12561,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O51" s="5" t="n">
+        <v>0.000614</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -13048,15 +12598,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cash flows from investing activity</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Share subscriptions received from option exercises</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Total cash provided by (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -13087,28 +12641,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K52" s="5" t="n">
-        <v>0.0623</v>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M52" s="5" t="n">
+        <v>-0.059516</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0.001901</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>-0.181089</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -13144,15 +12694,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cash flows from investing activity</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents during the year</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Total cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -13178,11 +12732,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J53" s="5" t="n">
-        <v>-0.043155</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>-0.036887</v>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -13199,10 +12757,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O53" s="5" t="n">
+        <v>0.198287</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -13238,59 +12794,43 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cash flows from investing activity</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Interest receivable</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F54" s="5" t="n">
+        <v>-0.003036</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.000648</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.000405</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>-8.4e-05</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>0.243757</v>
+        <v>0.000225</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0.200602</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001217</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0.000436</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.000189</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -13336,19 +12876,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cash flows from investing activity</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Interest received $</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -13375,20 +12911,16 @@
         </is>
       </c>
       <c r="J55" s="5" t="n">
-        <v>0.200602</v>
+        <v>0.002808</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.163715</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001714</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.000894</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.00024</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -13434,12 +12966,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Cash flows from (used in) operating activities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Interest received $</t>
+          <t>Recovery of office and administration expense</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -13468,16 +13000,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J56" s="5" t="n">
-        <v>0.002808</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>0.001714</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>-0.00105</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -13528,12 +13062,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities                                        (1,823)               (884))</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Due to related party</t>
+          <t>Due to related parties</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -13547,36 +13081,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G57" s="5" t="n">
+        <v>0.01232</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>0.01274</v>
       </c>
-      <c r="I57" s="5" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>-0.00281</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-0.02357</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0.002687</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -13622,7 +13148,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities                                        (1,823)               (884))</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -13631,20 +13157,14 @@
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="5" t="n">
+        <v>-0.000851</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>-0.084343</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.024223</v>
       </c>
       <c r="H58" s="5" t="n">
         <v>-0.03206</v>
@@ -13652,25 +13172,17 @@
       <c r="I58" s="5" t="n">
         <v>-0.021361</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J58" s="5" t="n">
+        <v>-0.043155</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>-0.099187</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-0.104178</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>-0.059516</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -13716,19 +13228,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities                                        (1,823)               (884))</t>
+          <t>Cash flows from investing activity</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Share subscriptions received from option exercises</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -13744,21 +13252,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H59" s="5" t="n">
-        <v>0.297178</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>0.265118</v>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K59" s="5" t="n">
+        <v>0.0623</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -13814,19 +13324,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities                                        (1,823)               (884))</t>
+          <t>Cash flows from investing activity</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Change in cash and cash equivalents during the year</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -13842,26 +13348,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H60" s="5" t="n">
-        <v>0.265118</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>0.243757</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>-0.043155</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>-0.036887</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>-0.104178</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -13912,15 +13416,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital balances</t>
+          <t>Cash flows from investing activity</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Interest Receivable</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -13931,31 +13439,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n">
-        <v>0.000648</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>0.000405</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J61" s="5" t="n">
+        <v>0.243757</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>0.200602</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>0.163715</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -14004,18 +13510,30 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cash flows from investing activity</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>For the year ended January 31, 2012 and period from incorporation to January</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>0.002011</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -14032,20 +13550,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J62" s="5" t="n">
+        <v>0.200602</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0.163715</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0.059537</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -14096,39 +13608,35 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) operating activities</t>
+          <t>Accounts payable and accrued liabilities                                        (1,823)               (884))</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>-0.000851</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>-0.130353</v>
+          <t>Due to related party</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H63" s="5" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>0.0126</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -14194,41 +13702,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) operating activities</t>
+          <t>Accounts payable and accrued liabilities                                        (1,823)               (884))</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Total cash outflows from operating activities</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>0.047628</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H64" s="5" t="n">
+        <v>-0.03206</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>-0.021361</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -14294,37 +13796,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital balances</t>
+          <t>Accounts payable and accrued liabilities                                        (1,823)               (884))</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HST receivable</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F65" s="5" t="n">
-        <v>-0.005611</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H65" s="5" t="n">
+        <v>0.297178</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.265118</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -14390,35 +13894,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) financing activities</t>
+          <t>Accounts payable and accrued liabilities                                        (1,823)               (884))</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Share capital proceeds</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.32781</v>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H66" s="5" t="n">
+        <v>0.265118</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.243757</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -14484,36 +13992,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) financing activities</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Interest Receivable</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="5" t="n">
-        <v>-0.01707</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.000648</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.000405</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -14584,27 +14086,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) financing activities</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Advance from a related party</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>0.000855</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>HST receivable</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>-0.005611</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.000491</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -14680,25 +14184,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) financing activities</t>
+          <t>Total cash inflows from financing activities                                                         -)            310,740)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Total cash inflows from financing activities</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>0.095855</v>
+          <t>Increase (decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.31074</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.226397</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>-0.024223</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -14774,29 +14282,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) financing activities</t>
+          <t>Total cash inflows from financing activities                                                         -)            310,740)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="n">
         <v>0.09500400000000001</v>
       </c>
-      <c r="F70" s="5" t="n">
-        <v>0.226397</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G70" s="5" t="n">
+        <v>0.321401</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -14872,17 +14380,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) financing activities</t>
+          <t>Total cash inflows from financing activities                                                         -)            310,740)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of period</t>
+          <t>Cash and cash equivalents, end of year $</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -14891,12 +14399,10 @@
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.09500400000000001</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.321401</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.297178</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -14970,26 +14476,18 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Cash flows from (used in) financing activities</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of period $</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>For the year ended January 31, 2012 and period from incorporation to January</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" s="5" t="n">
-        <v>0.09500400000000001</v>
+        <v>0.002011</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.321401</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -15065,49 +14563,59 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from (used in) operating activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Accounting and audit $</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>-0.000851</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>-0.130353</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H73" s="5" t="n">
-        <v>0.010249</v>
-      </c>
-      <c r="I73" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="J73" s="5" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="K73" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>0.009900000000000001</v>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -15124,48 +14632,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P73" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="Q73" s="5" t="n">
-        <v>0.01155</v>
-      </c>
-      <c r="R73" s="5" t="n">
-        <v>0.00941</v>
-      </c>
-      <c r="S73" s="5" t="n">
-        <v>0.018615</v>
-      </c>
-      <c r="T73" s="5" t="n">
-        <v>0.0137</v>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from (used in) operating activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Legal (recovery)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" s="5" t="n">
+        <v>0.047628</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -15227,8 +14747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S74" s="5" t="n">
-        <v>-0.000188</v>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -15239,33 +14761,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital proceeds</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.32781</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -15327,32 +14841,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S75" s="5" t="n">
-        <v>0.009067</v>
-      </c>
-      <c r="T75" s="5" t="n">
-        <v>0.017465</v>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Office and administration</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -15360,10 +14878,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" s="5" t="n">
+        <v>-0.01707</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -15410,47 +14926,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P76" s="5" t="n">
-        <v>0.000145</v>
-      </c>
-      <c r="Q76" s="5" t="n">
-        <v>0.000116</v>
-      </c>
-      <c r="R76" s="5" t="n">
-        <v>7.3e-05</v>
-      </c>
-      <c r="S76" s="5" t="n">
-        <v>0.002112</v>
-      </c>
-      <c r="T76" s="5" t="n">
-        <v>0.001497</v>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Advance from a related party</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>0.000855</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -15472,14 +14992,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J77" s="5" t="n">
-        <v>-0.044342</v>
-      </c>
-      <c r="K77" s="5" t="n">
-        <v>-0.094814</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>-0.122897</v>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -15496,66 +15022,84 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P77" s="5" t="n">
-        <v>-0.025496</v>
-      </c>
-      <c r="Q77" s="5" t="n">
-        <v>-0.025434</v>
-      </c>
-      <c r="R77" s="5" t="n">
-        <v>-0.023208</v>
-      </c>
-      <c r="S77" s="5" t="n">
-        <v>-0.029606</v>
-      </c>
-      <c r="T77" s="5" t="n">
-        <v>-0.032662</v>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Total cash inflows from financing activities</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="n">
-        <v>-3.2e-07</v>
+        <v>0.095855</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="K78" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.31074</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -15572,66 +15116,88 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="T78" s="5" t="n">
-        <v>0</v>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Increase in cash</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0.002684</v>
+        <v>0.09500400000000001</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>2.758766</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>3.139052</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>2.843162</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>2.139052</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>2.139052</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>2.139052</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>2.382278</v>
+        <v>0.226397</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -15648,48 +15214,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P79" s="5" t="n">
-        <v>5.225276</v>
-      </c>
-      <c r="Q79" s="5" t="n">
-        <v>5.225276</v>
-      </c>
-      <c r="R79" s="5" t="n">
-        <v>5.225276</v>
-      </c>
-      <c r="S79" s="5" t="n">
-        <v>5.225276</v>
-      </c>
-      <c r="T79" s="5" t="n">
-        <v>7.017542</v>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Equity $ (62,257) (29,606) (91,863) 107,950</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of period</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="5" t="n">
+        <v>0.09500400000000001</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -15751,39 +15329,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S80" s="5" t="n">
-        <v>-0.016575</v>
-      </c>
-      <c r="T80" s="5" t="n">
-        <v>-0.032662</v>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>$ Deficit (775,598) (29,606) (805,204)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, end of period $</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0.09500400000000001</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.321401</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -15845,11 +15427,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S81" s="5" t="n">
-        <v>-0.837866</v>
-      </c>
-      <c r="T81" s="5" t="n">
-        <v>-0.032662</v>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -15860,12 +15446,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>- total</t>
+          <t>Accounting and audit $</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -15884,70 +15470,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H82" s="5" t="n">
+        <v>0.010249</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>0.010133</v>
+      </c>
+      <c r="N82" s="5" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="P82" s="5" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="Q82" s="5" t="n">
+        <v>0.01155</v>
+      </c>
+      <c r="R82" s="5" t="n">
+        <v>0.00941</v>
+      </c>
+      <c r="S82" s="5" t="n">
+        <v>0.018615</v>
+      </c>
+      <c r="T82" s="5" t="n">
+        <v>0.0137</v>
       </c>
     </row>
     <row r="83">
@@ -15963,39 +15523,49 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Legal (recovery)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>0.035118</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>0.013053</v>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>0.015904</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>0.010736</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>0.00729</v>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>0.010303</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>0.010446</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -16012,17 +15582,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P83" s="5" t="n">
-        <v>0.01284</v>
-      </c>
-      <c r="Q83" s="5" t="n">
-        <v>0.013254</v>
-      </c>
-      <c r="R83" s="5" t="n">
-        <v>0.013725</v>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S83" s="5" t="n">
-        <v>0.009067</v>
+        <v>-0.000188</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -16043,12 +15619,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -16056,26 +15632,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>0.020831</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>0.005221</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>0.01096</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>0.004446</v>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>0.010562</v>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>0.045525</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>0.103206</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -16092,26 +15682,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P84" s="5" t="n">
-        <v>0.004011</v>
-      </c>
-      <c r="Q84" s="5" t="n">
-        <v>0.000514</v>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S84" s="5" t="n">
+        <v>0.009067</v>
+      </c>
+      <c r="T84" s="5" t="n">
+        <v>0.017465</v>
       </c>
     </row>
     <row r="85">
@@ -16127,10 +15717,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Equity $ (13,615) (25,434) (39,049)</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Office and administration</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -16171,41 +15765,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M85" s="5" t="n">
+        <v>0.000141</v>
+      </c>
+      <c r="N85" s="5" t="n">
+        <v>9.899999999999999e-05</v>
+      </c>
+      <c r="O85" s="5" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="P85" s="5" t="n">
+        <v>0.000145</v>
       </c>
       <c r="Q85" s="5" t="n">
-        <v>-0.062257</v>
+        <v>0.000116</v>
       </c>
       <c r="R85" s="5" t="n">
-        <v>-0.023208</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.3e-05</v>
+      </c>
+      <c r="S85" s="5" t="n">
+        <v>0.002112</v>
+      </c>
+      <c r="T85" s="5" t="n">
+        <v>0.001497</v>
       </c>
     </row>
     <row r="86">
@@ -16216,15 +15798,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>$ Deficit (726,956) (25,434) (752,390)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -16250,56 +15836,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J86" s="5" t="n">
+        <v>-0.044342</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>-0.094814</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>-0.122897</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>-0.069337</v>
+      </c>
+      <c r="N86" s="5" t="n">
+        <v>-0.06632399999999999</v>
+      </c>
+      <c r="O86" s="5" t="n">
+        <v>-0.051961</v>
+      </c>
+      <c r="P86" s="5" t="n">
+        <v>-0.025496</v>
       </c>
       <c r="Q86" s="5" t="n">
-        <v>-0.775598</v>
+        <v>-0.025434</v>
       </c>
       <c r="R86" s="5" t="n">
         <v>-0.023208</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S86" s="5" t="n">
+        <v>-0.029606</v>
+      </c>
+      <c r="T86" s="5" t="n">
+        <v>-0.032662</v>
       </c>
     </row>
     <row r="87">
@@ -16310,94 +15878,66 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Total total</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>-3.2e-07</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="N87" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="O87" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="P87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="T87" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -16413,85 +15953,61 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Equity $ 11,881 (25,496) (13,615)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.002684</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>2.758766</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>3.139052</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>2.843162</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>2.139052</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>2.139052</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>2.139052</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>2.382278</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>1.225276</v>
+      </c>
+      <c r="N88" s="5" t="n">
+        <v>1.225276</v>
+      </c>
+      <c r="O88" s="5" t="n">
+        <v>2.099593</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>-0.039049</v>
+        <v>5.225276</v>
       </c>
       <c r="Q88" s="5" t="n">
-        <v>-0.025434</v>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.225276</v>
+      </c>
+      <c r="R88" s="5" t="n">
+        <v>5.225276</v>
+      </c>
+      <c r="S88" s="5" t="n">
+        <v>5.225276</v>
+      </c>
+      <c r="T88" s="5" t="n">
+        <v>7.017542</v>
       </c>
     </row>
     <row r="89">
@@ -16502,12 +16018,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>$ Deficit (701,460) (25,496) (726,956)</t>
+          <t>Equity $ (62,257) (29,606) (91,863) 107,950</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -16566,26 +16082,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P89" s="5" t="n">
-        <v>-0.75239</v>
-      </c>
-      <c r="Q89" s="5" t="n">
-        <v>-0.025434</v>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S89" s="5" t="n">
+        <v>-0.016575</v>
+      </c>
+      <c r="T89" s="5" t="n">
+        <v>-0.032662</v>
       </c>
     </row>
     <row r="90">
@@ -16596,12 +16112,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Office and administration (recovery) 5</t>
+          <t>$ Deficit (775,598) (29,606) (805,204)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -16635,11 +16151,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K90" s="5" t="n">
-        <v>0.0264</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>-0.000197</v>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -16671,15 +16191,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S90" s="5" t="n">
+        <v>-0.837866</v>
+      </c>
+      <c r="T90" s="5" t="n">
+        <v>-0.032662</v>
       </c>
     </row>
     <row r="91">
@@ -16690,12 +16206,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Travel and entertainment</t>
+          <t>- total</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -16724,11 +16240,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J91" s="5" t="n">
-        <v>0.007960999999999999</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>0.001266</v>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -16789,72 +16309,60 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Loss before other item</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>-0.000851</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-0.133389</v>
+        <v>0.035118</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-0.044444</v>
+        <v>0.013053</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>-0.049905</v>
+        <v>0.015904</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.035867</v>
+        <v>0.010736</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.046927</v>
+        <v>0.00729</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.095494</v>
+        <v>0.010303</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>-0.123355</v>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010446</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>0.009974</v>
+      </c>
+      <c r="N92" s="5" t="n">
+        <v>0.014977</v>
+      </c>
+      <c r="O92" s="5" t="n">
+        <v>0.011329</v>
+      </c>
+      <c r="P92" s="5" t="n">
+        <v>0.01284</v>
+      </c>
+      <c r="Q92" s="5" t="n">
+        <v>0.013254</v>
+      </c>
+      <c r="R92" s="5" t="n">
+        <v>0.013725</v>
+      </c>
+      <c r="S92" s="5" t="n">
+        <v>0.009067</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -16875,12 +16383,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -16889,50 +16397,40 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.003036</v>
+        <v>0.020831</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.003653</v>
+        <v>0.005221</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.003007</v>
+        <v>0.01096</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.002975</v>
+        <v>0.004446</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>0.002585</v>
+        <v>0.010562</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>0.00068</v>
+        <v>0.045525</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>0.000458</v>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.103206</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>0.04914</v>
+      </c>
+      <c r="N93" s="5" t="n">
+        <v>0.042848</v>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>0.029942</v>
+      </c>
+      <c r="P93" s="5" t="n">
+        <v>0.004011</v>
+      </c>
+      <c r="Q93" s="5" t="n">
+        <v>0.000514</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -16963,34 +16461,44 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Office and administration 5</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>0.000851</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>0.011906</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>0.012756</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>0.012792</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>0.013185</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>0.012114</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>0.0264</v>
+          <t>Equity $ (13,615) (25,434) (39,049)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -17017,15 +16525,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q94" s="5" t="n">
+        <v>-0.062257</v>
+      </c>
+      <c r="R94" s="5" t="n">
+        <v>-0.023208</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -17046,12 +16550,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Travel and Entertainment</t>
+          <t>$ Deficit (726,956) (25,434) (752,390)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -17080,8 +16584,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J95" s="5" t="n">
-        <v>0.007960999999999999</v>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -17113,15 +16619,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q95" s="5" t="n">
+        <v>-0.775598</v>
+      </c>
+      <c r="R95" s="5" t="n">
+        <v>-0.023208</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17142,36 +16644,44 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>-0.000851</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>-0.130353</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>-0.040791</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>-0.046898</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>-0.032892</v>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>-0.044342</v>
+          <t>Total total</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -17232,12 +16742,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>(171,995)         (46,898) -          (218,893)         (32,892)          (251,785)                                                              Deficit</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>(171,995)         (46,898) -          (218,893)         (32,892)          (251,785)                                                              Deficit $</t>
+          <t>Equity $ 11,881 (25,496) (13,615)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -17256,8 +16766,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H97" s="5" t="n">
-        <v>0.00583</v>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -17294,15 +16806,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P97" s="5" t="n">
+        <v>-0.039049</v>
+      </c>
+      <c r="Q97" s="5" t="n">
+        <v>-0.025434</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -17328,12 +16836,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Warrants        Reserve</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Warrants        Reserve statements. Reserves -</t>
+          <t>$ Deficit (701,460) (25,496) (726,956)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -17392,15 +16900,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P98" s="5" t="n">
+        <v>-0.75239</v>
+      </c>
+      <c r="Q98" s="5" t="n">
+        <v>-0.025434</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -17426,12 +16930,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>are              of       -     -                            Share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Shares notes Number 3,139,052 (1,000,000)</t>
+          <t>Equity $ (2,327) 11,881 200,000 (51,961) (25,496)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -17450,11 +16954,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="5" t="n">
-        <v>2.139052</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>2.139052</v>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -17481,15 +16989,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O99" s="5" t="n">
+        <v>-0.133831</v>
+      </c>
+      <c r="P99" s="5" t="n">
+        <v>-0.013615</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -17520,12 +17024,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Accounting $</t>
+          <t>$ Deficit (649,499) (51,961) (701,460)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -17534,14 +17038,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F100" s="5" t="n">
-        <v>0.01565</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>0.01135</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>0.010249</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -17573,15 +17083,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O100" s="5" t="n">
+        <v>-0.726956</v>
+      </c>
+      <c r="P100" s="5" t="n">
+        <v>-0.025496</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -17617,12 +17123,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Loss before other items</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -17630,11 +17136,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F101" s="5" t="n">
-        <v>0.000606</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>0.002064</v>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17661,15 +17171,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M101" s="5" t="n">
+        <v>-0.06938800000000001</v>
+      </c>
+      <c r="N101" s="5" t="n">
+        <v>-0.06632399999999999</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -17715,52 +17221,42 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>(40,791) 281,373 (46,898) 234,475 Equity $</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="5" t="n">
+        <v>0.003036</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.003653</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0.322164</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003007</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>0.002975</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>0.002585</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>0.00068</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>0.000458</v>
+      </c>
+      <c r="M102" s="5" t="n">
+        <v>5.1e-05</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -17806,12 +17302,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>$                                                                                                       (131,204)      (40,791)       (171,995)      (46,898)                      (218,893)                                                            Deficit</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>$                                                                                                       (131,204)      (40,791)       (171,995)      (46,898)                      (218,893)                                                            Deficit</t>
+          <t>Equity $ 1,830 (69,337) (67,507)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -17825,11 +17321,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G103" s="5" t="n">
-        <v>0.00583</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>0.00583</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -17851,15 +17351,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M103" s="5" t="n">
+        <v>-0.133831</v>
+      </c>
+      <c r="N103" s="5" t="n">
+        <v>-0.06632399999999999</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -17900,12 +17396,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>$                                                           Warrants Reserve                                                                                                                                                                                                                                                                                                                                                                                                                  statements.</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Reserves -</t>
+          <t>$ Deficit (513,838) (69,337) (583,175)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -17949,15 +17445,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M104" s="5" t="n">
+        <v>-0.649499</v>
+      </c>
+      <c r="N104" s="5" t="n">
+        <v>-0.06632399999999999</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -18003,7 +17495,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Geological services</t>
+          <t>Office and administration (recovery)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -18012,8 +17504,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>0.00165</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -18040,15 +17534,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L105" s="5" t="n">
+        <v>-0.000655</v>
+      </c>
+      <c r="M105" s="5" t="n">
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -18099,24 +17589,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Office and administration 7</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Office and administration (recovery) 5</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F106" s="5" t="n">
-        <v>0.011906</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>0.012756</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -18133,15 +17623,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K106" s="5" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>-0.000197</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -18197,7 +17683,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Travel and entertainment</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -18206,8 +17692,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F107" s="5" t="n">
-        <v>0.047628</v>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -18224,15 +17712,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J107" s="5" t="n">
+        <v>0.007960999999999999</v>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>0.001266</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -18293,45 +17777,37 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss before other item</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>-0.000851</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>-0.000851</v>
+        <v>-0.133389</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>-0.131204</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.044444</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>-0.049905</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>-0.035867</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>-0.046927</v>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>-0.095494</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>-0.123355</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -18387,38 +17863,34 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Deficit, end of year $</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Office and administration 5</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
-        <v>-0.000851</v>
+        <v>0.000851</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>-0.131204</v>
+        <v>0.011906</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>-0.171995</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012756</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0.012792</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0.013185</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>0.012114</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>0.0264</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -18479,7 +17951,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Equity 94,149 4,810 47,628 8,336 - 323,000 (25,406) 358,368 322,164 (40,791)</t>
+          <t>Travel and Entertainment</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -18488,11 +17960,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F110" s="5" t="n">
-        <v>-0.130353</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>0.281373</v>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -18504,10 +17980,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J110" s="5" t="n">
+        <v>0.007960999999999999</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -18568,44 +18042,36 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Total $                $</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>-0.000851</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>-0.130353</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>-0.040791</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>-0.046898</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>-0.032892</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>-0.044342</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -18664,85 +18130,1519 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>(171,995)         (46,898) -          (218,893)         (32,892)          (251,785)                                                              Deficit</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
+          <t>(171,995)         (46,898) -          (218,893)         (32,892)          (251,785)                                                              Deficit $</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>0.00583</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Warrants        Reserve</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Warrants        Reserve statements. Reserves -</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>are              of       -     -                            Share</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Shares notes Number 3,139,052 (1,000,000)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>2.139052</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>2.139052</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Accounting $</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0.01565</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.01135</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0.010249</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0.000606</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.002064</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>(40,791) 281,373 (46,898) 234,475 Equity $</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>0.322164</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>$                                                                                                       (131,204)      (40,791)       (171,995)      (46,898)                      (218,893)                                                            Deficit</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>$                                                                                                       (131,204)      (40,791)       (171,995)      (46,898)                      (218,893)                                                            Deficit</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.00583</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>0.00583</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>$                                                           Warrants Reserve                                                                                                                                                                                                                                                                                                                                                                                                                  statements.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Reserves -</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Geological services</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.00165</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Office and administration 7</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.011906</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.012756</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.047628</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>-0.000851</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>-0.131204</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Deficit, end of year $</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>-0.000851</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>-0.131204</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>-0.171995</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Equity 94,149 4,810 47,628 8,336 - 323,000 (25,406) 358,368 322,164 (40,791)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>-0.130353</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.281373</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Total $                $</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
           <t>For the year ended January 31, 2012 and period from incorporation to January</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" s="5" t="n">
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" s="5" t="n">
         <v>0.002011</v>
       </c>
-      <c r="F112" s="5" t="n">
+      <c r="F127" s="5" t="n">
         <v>3.1e-05</v>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T112" t="inlineStr">
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
